--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484752_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484752_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3437</v>
+        <v>4.5059</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7892</v>
+        <v>3.9249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5545</v>
+        <v>0.581</v>
       </c>
       <c r="G2" t="n">
         <v>1.4521</v>
@@ -610,13 +610,13 @@
         <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>5.9936</v>
+        <v>3.1558</v>
       </c>
       <c r="T2" t="n">
-        <v>5.6631</v>
+        <v>2.7989</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3305</v>
+        <v>0.3569</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6681</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1619</v>
+        <v>3.6175</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4513</v>
+        <v>4.5101</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2894</v>
+        <v>-0.8925999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0.7648</v>
@@ -688,13 +688,13 @@
         <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4613</v>
+        <v>1.9169</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7658</v>
+        <v>1.8246</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3045</v>
+        <v>0.0924</v>
       </c>
       <c r="V3" t="n">
         <v>0.9358</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9485</v>
+        <v>0.3374</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5977</v>
+        <v>0.0131</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3507</v>
+        <v>0.3243</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5094</v>
@@ -766,13 +766,13 @@
         <v>0.1887</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2691</v>
+        <v>0.6581</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1228</v>
+        <v>0.5382</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1464</v>
+        <v>0.1199</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. MOLLERMARK</t>
+          <t>G. MEJÍA ACOSTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4074</v>
+        <v>0.317</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3864</v>
+        <v>0.317</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.979</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0247</v>
+        <v>0.317</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1268</v>
+        <v>0.317</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1515</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.972</v>
+        <v>0.317</v>
       </c>
       <c r="K5" t="n">
-        <v>0.972</v>
+        <v>0.317</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9967</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8452</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1515</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4144</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0176</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>R. MOLLERMARK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3232</v>
+        <v>0.0441</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0184</v>
+        <v>0.9967</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3048</v>
+        <v>-0.9526</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7328</v>
+        <v>-0.0247</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2262</v>
+        <v>0.1268</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5066000000000001</v>
+        <v>-0.1515</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3936</v>
+        <v>0.972</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8616</v>
+        <v>0.972</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.468</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3392</v>
+        <v>-0.9967</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6354</v>
+        <v>-0.8452</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9746</v>
+        <v>-0.1515</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9435</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9944</v>
+        <v>0.0688</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4176</v>
+        <v>0.0247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5768</v>
+        <v>0.0441</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.517</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.9624</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5546</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. MEJÍA ACOSTA</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.317</v>
+        <v>-0.2377</v>
       </c>
       <c r="E7" t="n">
-        <v>0.317</v>
+        <v>0.6279</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.8656</v>
       </c>
       <c r="G7" t="n">
-        <v>0.317</v>
+        <v>0.6564</v>
       </c>
       <c r="H7" t="n">
-        <v>0.317</v>
+        <v>0.36</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.2964</v>
       </c>
       <c r="J7" t="n">
-        <v>0.317</v>
+        <v>1.134</v>
       </c>
       <c r="K7" t="n">
-        <v>0.317</v>
+        <v>1.141</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.0071</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-0.4775</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.781</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.3035</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.1624</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.4374</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2751</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3095</v>
+        <v>-0.9808</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4439</v>
+        <v>-0.9946</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8656</v>
+        <v>0.0138</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6564</v>
+        <v>0.7328</v>
       </c>
       <c r="H8" t="n">
-        <v>0.36</v>
+        <v>0.2262</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2964</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.134</v>
+        <v>0.3936</v>
       </c>
       <c r="K8" t="n">
-        <v>1.141</v>
+        <v>0.8616</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0071</v>
+        <v>-0.468</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4775</v>
+        <v>0.3392</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.781</v>
+        <v>-0.6354</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3035</v>
+        <v>0.9746</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9094</v>
+        <v>2.6904</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6343</v>
+        <v>2.4046</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2751</v>
+        <v>0.2858</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2452</v>
+        <v>-2.517</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.9624</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2452</v>
+        <v>-1.5546</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. MALONE NAVARRO</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9482</v>
+        <v>-1.4553</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8425</v>
+        <v>-1.358</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1058</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5555</v>
+        <v>-0.4134</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6638</v>
+        <v>-0.781</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1083</v>
+        <v>0.3676</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6073</v>
+        <v>-1.0452</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6073</v>
+        <v>-0.4383</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9482</v>
+        <v>0.6318</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0565</v>
+        <v>-0.3428</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1083</v>
+        <v>0.9746</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0412</v>
+        <v>1.0146</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2352</v>
+        <v>0.6307</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2763</v>
+        <v>0.3839</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6226</v>
+        <v>-1.8678</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6226</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>B. MALONE NAVARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0142</v>
+        <v>-1.7798</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.917</v>
+        <v>-0.6476</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-1.1322</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4134</v>
+        <v>-1.5555</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.781</v>
+        <v>-1.6638</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3676</v>
+        <v>0.1083</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0452</v>
+        <v>-0.6073</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4383</v>
+        <v>-0.6073</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.607</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6318</v>
+        <v>-0.9482</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3428</v>
+        <v>-1.0565</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9746</v>
+        <v>0.1083</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5443</v>
+        <v>0.2096</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9283</v>
+        <v>-0.0403</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3839</v>
+        <v>0.2498</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8678</v>
+        <v>-0.6226</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8678</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.435</v>
+        <v>-3.9948</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7757</v>
+        <v>-1.2298</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6592</v>
+        <v>-2.765</v>
       </c>
       <c r="G11" t="n">
         <v>-4.1654</v>
@@ -1312,13 +1312,13 @@
         <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2286</v>
+        <v>1.6687</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7483</v>
+        <v>1.2942</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4803</v>
+        <v>0.3745</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9320000000000001</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.8272</v>
+        <v>-6.1121</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.1867</v>
+        <v>-3.4715</v>
       </c>
       <c r="F12" t="n">
         <v>-2.6405</v>
@@ -1390,10 +1390,10 @@
         <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0247</v>
+        <v>1.7398</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7272</v>
+        <v>0.9879</v>
       </c>
       <c r="U12" t="n">
         <v>0.7519</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.032399999999999</v>
+        <v>-5.738599999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3942</v>
+        <v>2.688200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.426699999999999</v>
+        <v>-8.426600000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-8.9861</v>
@@ -1441,7 +1441,7 @@
         <v>-1.1914</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3930000000000016</v>
+        <v>0.3929999999999998</v>
       </c>
       <c r="K13" t="n">
         <v>1.478900000000001</v>
@@ -1453,13 +1453,13 @@
         <v>-9.3787</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.273500000000002</v>
+        <v>-9.2735</v>
       </c>
       <c r="O13" t="n">
         <v>-0.1052</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9435</v>
+        <v>-0.9434999999999998</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.3785</v>
@@ -1468,10 +1468,10 @@
         <v>9.435</v>
       </c>
       <c r="S13" t="n">
-        <v>12.9912</v>
+        <v>13.2851</v>
       </c>
       <c r="T13" t="n">
-        <v>10.607</v>
+        <v>10.9009</v>
       </c>
       <c r="U13" t="n">
         <v>2.3841</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9679</v>
+        <v>6.9511</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1872</v>
+        <v>9.9923</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2193</v>
+        <v>-3.0412</v>
       </c>
       <c r="G14" t="n">
         <v>4.7485</v>
@@ -1546,13 +1546,13 @@
         <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2297</v>
+        <v>-1.2465</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0769</v>
+        <v>-0.1179</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3067</v>
+        <v>-1.1286</v>
       </c>
       <c r="V14" t="n">
         <v>1.9396</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4784</v>
+        <v>5.1159</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0008</v>
+        <v>4.1956</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4776</v>
+        <v>0.9203</v>
       </c>
       <c r="G15" t="n">
         <v>6.4158</v>
@@ -1624,13 +1624,13 @@
         <v>1.3209</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.3866</v>
+        <v>-1.7491</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7642</v>
+        <v>-0.5694</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6224</v>
+        <v>-1.1797</v>
       </c>
       <c r="V15" t="n">
         <v>0.0717</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5762</v>
+        <v>2.9057</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7029</v>
+        <v>2.5081</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1268</v>
+        <v>0.3976</v>
       </c>
       <c r="G16" t="n">
         <v>2.8177</v>
@@ -1702,13 +1702,13 @@
         <v>2.0757</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9581</v>
+        <v>-1.6286</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1582</v>
+        <v>-0.3531</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.7999</v>
+        <v>-1.2755</v>
       </c>
       <c r="V16" t="n">
         <v>2.4714</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8844</v>
+        <v>1.9874</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0219</v>
+        <v>0.3142</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8625</v>
+        <v>1.6731</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8283</v>
@@ -1780,13 +1780,13 @@
         <v>1.6983</v>
       </c>
       <c r="S17" t="n">
-        <v>-3.2273</v>
+        <v>-2.1243</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6902</v>
+        <v>-0.3979</v>
       </c>
       <c r="U17" t="n">
-        <v>-2.5371</v>
+        <v>-1.7264</v>
       </c>
       <c r="V17" t="n">
         <v>3.2417</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3359</v>
+        <v>0.283</v>
       </c>
       <c r="E18" t="n">
         <v>0.4626</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1267</v>
+        <v>-0.1796</v>
       </c>
       <c r="G18" t="n">
         <v>0.1483</v>
@@ -1858,13 +1858,13 @@
         <v>0.1887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0012</v>
+        <v>-0.0541</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0012</v>
+        <v>-0.0541</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1687</v>
+        <v>0.1951</v>
       </c>
       <c r="E19" t="n">
         <v>0.0211</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1475</v>
+        <v>0.174</v>
       </c>
       <c r="G19" t="n">
         <v>0.151</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SERNEGUET GARVI</t>
+          <t>C. SEVERA LENCINA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.2885</v>
+        <v>-4.1033</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.536</v>
+        <v>-4.3365</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2474</v>
+        <v>0.2332</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1988</v>
+        <v>-1.057</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5104</v>
+        <v>-0.0313</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6883</v>
+        <v>-1.0257</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1531</v>
+        <v>-0.8544</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3774</v>
+        <v>0.2802</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7756</v>
+        <v>-1.1346</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0457</v>
+        <v>-0.2026</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.133</v>
+        <v>-0.3114</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0873</v>
+        <v>0.1089</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.8305</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6983</v>
+        <v>1.887</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2556</v>
+        <v>-2.1746</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0994</v>
+        <v>-0.6516</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1561</v>
+        <v>-1.523</v>
       </c>
       <c r="V21" t="n">
-        <v>1.298</v>
+        <v>0.0717</v>
       </c>
       <c r="W21" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.249</v>
+        <v>0.0717</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. SEVERA LENCINA</t>
+          <t>A. SERNEGUET GARVI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8791</v>
+        <v>-4.4929</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.4339</v>
+        <v>-4.7309</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4452</v>
+        <v>0.238</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.057</v>
+        <v>-3.1988</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0313</v>
+        <v>-1.5104</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0257</v>
+        <v>-1.6883</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8544</v>
+        <v>-3.1531</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2802</v>
+        <v>-1.3774</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1346</v>
+        <v>-1.7756</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2026</v>
+        <v>-0.0457</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3114</v>
+        <v>-0.133</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1089</v>
+        <v>0.0873</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.8305</v>
       </c>
       <c r="R22" t="n">
-        <v>1.887</v>
+        <v>1.6983</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.9504</v>
+        <v>-1.4599</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.749</v>
+        <v>-0.2943</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.2014</v>
+        <v>-1.1656</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0717</v>
+        <v>1.298</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0717</v>
+        <v>-0.249</v>
       </c>
     </row>
     <row r="23">
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.0326</v>
+        <v>8.630700000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>8.426600000000001</v>
+        <v>8.426499999999997</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3943</v>
+        <v>0.2041000000000002</v>
       </c>
       <c r="G23" t="n">
         <v>8.985900000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>7.7948</v>
+        <v>7.794800000000001</v>
       </c>
       <c r="I23" t="n">
         <v>1.1914</v>
@@ -2224,13 +2224,13 @@
         <v>9.3787</v>
       </c>
       <c r="K23" t="n">
-        <v>9.273500000000002</v>
+        <v>9.2735</v>
       </c>
       <c r="L23" t="n">
         <v>0.1051999999999995</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3928999999999999</v>
+        <v>-0.3929</v>
       </c>
       <c r="N23" t="n">
         <v>-1.4788</v>
@@ -2239,7 +2239,7 @@
         <v>1.0862</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9434999999999996</v>
+        <v>0.9434999999999998</v>
       </c>
       <c r="Q23" t="n">
         <v>-9.434999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>10.3785</v>
       </c>
       <c r="S23" t="n">
-        <v>-12.9913</v>
+        <v>-10.393</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.3841</v>
+        <v>-2.3842</v>
       </c>
       <c r="U23" t="n">
-        <v>-10.6072</v>
+        <v>-8.008799999999999</v>
       </c>
       <c r="V23" t="n">
         <v>9.094099999999999</v>
